--- a/reports/jobs_2026-09-17.xlsx
+++ b/reports/jobs_2026-09-17.xlsx
@@ -520,12 +520,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Twilio India</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software Engineer Intern (January 12th start, 23 weeks) </t>
+          <t>Developer (Vapasi) - Intern</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -535,12 +535,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1–5 years</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -550,12 +550,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8190889</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/twilio</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Product Management - Intern - Telco.</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/5648edd6-b73b-4156-96f5-343f4d851610</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Talent Acquisition Intern - Gurgaon</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Gurugram, Haryana</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Gurgaon</t>
+          <t>Visual Design Intern- Paytm</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/91ef4dc2-8cd8-427a-84cd-c9308753a203</t>
+          <t>https://jobs.lever.co/paytm/4f0b8508-1fae-45ae-bc09-67291ea3c447</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -3037,17 +3037,17 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Visual Design Intern- Paytm</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3055,11 +3055,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3067,12 +3063,12 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/4f0b8508-1fae-45ae-bc09-67291ea3c447</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
@@ -3084,17 +3080,17 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3102,7 +3098,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3221,17 +3221,17 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3239,11 +3239,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="inlineStr"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3251,12 +3247,12 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -3268,12 +3264,12 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -3286,7 +3282,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3452,17 +3452,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Remote Instructor- Python</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3499,17 +3499,17 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Sound Designer - AI</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3517,11 +3517,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>Remote Instructor- Python</t>
-        </is>
-      </c>
+      <c r="E67" s="4" t="inlineStr"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3529,12 +3525,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3551,7 +3547,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Sound Designer - AI</t>
+          <t>Creative Producer - AI</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3572,7 +3568,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NDEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3589,17 +3585,17 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Creative Producer - AI</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3607,7 +3603,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3615,12 +3615,12 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjQsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3679,17 +3679,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3697,11 +3697,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E71" s="4" t="inlineStr"/>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3709,12 +3705,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3726,12 +3722,12 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -3744,7 +3740,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-09-17</t>
@@ -3752,12 +3752,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3769,12 +3769,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Twilio India</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t xml:space="preserve">Software Engineer Intern (January 12th start, 23 weeks) </t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8190889</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://boards.greenhouse.io/twilio</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -4151,15 +4151,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Ather Energy</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.atherenergy.com/careers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4168,26 +4188,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ather Energy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.atherenergy.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -4211,35 +4211,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Darwinbox</t>
+          <t>Juspay</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://darwinbox.com/careers</t>
+          <t>https://juspay.io/careers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Juspay</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://juspay.io/careers</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4248,18 +4228,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4268,18 +4248,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>FirstCry</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.firstcry.com/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4288,6 +4268,26 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>OYO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.oyorooms.com/careers/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.oyorooms.com/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
